--- a/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
+++ b/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
+++ b/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
+++ b/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
+++ b/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
+++ b/docs/ValueSet-cognitive-performance-indicators-vs.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -25,13 +26,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/ValueSet/cognitive-performance-indicators-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/cognitive-performance-indicators-vs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,10 +56,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +95,9 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Immutable</t>
   </si>
   <si>
@@ -103,22 +110,28 @@
     <t>reaction-time-ms</t>
   </si>
   <si>
-    <t>hrv-ms</t>
-  </si>
-  <si>
     <t>activity-level</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/behavioral-biomarker-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/behavioral-biomarker-cs</t>
+  </si>
+  <si>
+    <t>80404-7</t>
+  </si>
+  <si>
+    <t>R-R interval.standard deviation (Heart rate variability)</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>cognitive-readiness</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/aerospace-behavioral-state-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/aerospace-behavioral-state-cs</t>
   </si>
 </sst>
 </file>
@@ -311,66 +324,70 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -380,7 +397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -389,44 +406,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -445,32 +456,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
